--- a/Excel/Project/Freshmart/Cleaned/Cleaned_FreshMart_Customers.xlsx
+++ b/Excel/Project/Freshmart/Cleaned/Cleaned_FreshMart_Customers.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnudipCOA\Desktop\Rithiha\Excel\Project\Freshmart\Cleaned\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/AB6FF4EDD41B64DB/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D989ED1-497B-4F3A-A677-CA2F8E25E141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{90D83587-37E6-4355-8B83-C173FE46D25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837063CB-87A7-445A-AA94-2546DA01C87D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{12744E2A-B81B-4B43-97B4-F1260E66F263}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{12744E2A-B81B-4B43-97B4-F1260E66F263}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Customers" sheetId="1" r:id="rId1"/>
     <sheet name="Data_Profiling" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6346" uniqueCount="2882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6348" uniqueCount="2884">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -8684,6 +8684,12 @@
   </si>
   <si>
     <t>Solved using mapping function</t>
+  </si>
+  <si>
+    <t>Fixed Using Replace</t>
+  </si>
+  <si>
+    <t>Changed Using VALUE() function</t>
   </si>
 </sst>
 </file>
@@ -8773,63 +8779,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -8975,6 +8924,63 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -9088,7 +9094,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB22DD0B-77A1-49AA-96FE-89CD34C1EE46}" name="Table1" displayName="Table1" ref="A1:N701" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB22DD0B-77A1-49AA-96FE-89CD34C1EE46}" name="Customer" displayName="Customer" ref="A1:N701" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N701" xr:uid="{AB22DD0B-77A1-49AA-96FE-89CD34C1EE46}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{AEBA8851-91EB-4F29-BACA-1089DA44B5F2}" name="Customer_ID" dataDxfId="13"/>
@@ -9097,20 +9103,20 @@
       <calculatedColumnFormula>TRIM(B2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{41DDE33D-22FC-4ABC-9BDF-0B0BB89D6028}" name="Gender" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{9A2E2228-5972-4CD1-AAC7-4F98199FF157}" name="DOB" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{29C3CD44-805F-4FB3-9AFB-DBA4BE04B3E1}" name="Phone" dataDxfId="0"/>
-    <tableColumn id="15" xr3:uid="{500887DF-FC33-47B2-8C33-06AD2A316C07}" name="Phone2" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{9A2E2228-5972-4CD1-AAC7-4F98199FF157}" name="DOB" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{29C3CD44-805F-4FB3-9AFB-DBA4BE04B3E1}" name="Phone" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{500887DF-FC33-47B2-8C33-06AD2A316C07}" name="Phone2" dataDxfId="7">
       <calculatedColumnFormula>VALUE(F2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0615E048-4BD4-4E9C-B84F-D0088E2B0E9A}" name="Email" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{8BF1EF82-7253-4F9F-BEEC-67314F662CF7}" name="City" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{87116D37-63CB-416A-9D1C-2AF8E91263D7}" name="State" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{325117A9-AD3A-46BF-AB5D-5F0228CC4885}" name="Region" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{DC38C0D8-6F03-40C1-964B-CE4B71300DF9}" name="Membership" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{9C2950FE-95B7-4AB7-8026-92829ED136E2}" name="Membership2" dataDxfId="4">
-      <calculatedColumnFormula>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{0615E048-4BD4-4E9C-B84F-D0088E2B0E9A}" name="Email" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{8BF1EF82-7253-4F9F-BEEC-67314F662CF7}" name="City" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{87116D37-63CB-416A-9D1C-2AF8E91263D7}" name="State" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{325117A9-AD3A-46BF-AB5D-5F0228CC4885}" name="Region" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{DC38C0D8-6F03-40C1-964B-CE4B71300DF9}" name="Membership" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{9C2950FE-95B7-4AB7-8026-92829ED136E2}" name="Membership2" dataDxfId="1">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{5A7A7640-4AB5-4FDC-87CB-249F0503BE7F}" name="Registration_Date" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{5A7A7640-4AB5-4FDC-87CB-249F0503BE7F}" name="Registration_Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9536,7 +9542,7 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N2" s="3">
@@ -9583,7 +9589,7 @@
         <v>25</v>
       </c>
       <c r="M3" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N3" s="3">
@@ -9630,7 +9636,7 @@
         <v>19</v>
       </c>
       <c r="M4" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N4" s="3">
@@ -9677,7 +9683,7 @@
         <v>25</v>
       </c>
       <c r="M5" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N5" s="3">
@@ -9724,7 +9730,7 @@
         <v>25</v>
       </c>
       <c r="M6" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N6" s="3">
@@ -9771,7 +9777,7 @@
         <v>25</v>
       </c>
       <c r="M7" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N7" s="3">
@@ -9818,7 +9824,7 @@
         <v>25</v>
       </c>
       <c r="M8" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N8" s="3">
@@ -9865,7 +9871,7 @@
         <v>25</v>
       </c>
       <c r="M9" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N9" s="3">
@@ -9912,7 +9918,7 @@
         <v>19</v>
       </c>
       <c r="M10" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N10" s="3">
@@ -9959,7 +9965,7 @@
         <v>19</v>
       </c>
       <c r="M11" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N11" s="3">
@@ -10006,7 +10012,7 @@
         <v>19</v>
       </c>
       <c r="M12" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N12" s="3">
@@ -10053,7 +10059,7 @@
         <v>19</v>
       </c>
       <c r="M13" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N13" s="3">
@@ -10100,7 +10106,7 @@
         <v>19</v>
       </c>
       <c r="M14" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N14" s="3">
@@ -10147,7 +10153,7 @@
         <v>25</v>
       </c>
       <c r="M15" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N15" s="3">
@@ -10194,7 +10200,7 @@
         <v>19</v>
       </c>
       <c r="M16" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N16" s="3">
@@ -10241,7 +10247,7 @@
         <v>19</v>
       </c>
       <c r="M17" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N17" s="3">
@@ -10288,7 +10294,7 @@
         <v>25</v>
       </c>
       <c r="M18" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N18" s="3">
@@ -10335,7 +10341,7 @@
         <v>25</v>
       </c>
       <c r="M19" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N19" s="3">
@@ -10382,7 +10388,7 @@
         <v>110</v>
       </c>
       <c r="M20" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N20" s="3">
@@ -10429,7 +10435,7 @@
         <v>19</v>
       </c>
       <c r="M21" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N21" s="3">
@@ -10476,7 +10482,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N22" s="3">
@@ -10523,7 +10529,7 @@
         <v>19</v>
       </c>
       <c r="M23" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N23" s="3">
@@ -10570,7 +10576,7 @@
         <v>25</v>
       </c>
       <c r="M24" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N24" s="3">
@@ -10617,7 +10623,7 @@
         <v>25</v>
       </c>
       <c r="M25" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N25" s="3">
@@ -10664,7 +10670,7 @@
         <v>19</v>
       </c>
       <c r="M26" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N26" s="3">
@@ -10711,7 +10717,7 @@
         <v>19</v>
       </c>
       <c r="M27" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N27" s="3">
@@ -10758,7 +10764,7 @@
         <v>25</v>
       </c>
       <c r="M28" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N28" s="3">
@@ -10805,7 +10811,7 @@
         <v>19</v>
       </c>
       <c r="M29" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N29" s="3">
@@ -10852,7 +10858,7 @@
         <v>25</v>
       </c>
       <c r="M30" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N30" s="3">
@@ -10899,7 +10905,7 @@
         <v>25</v>
       </c>
       <c r="M31" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N31" s="3">
@@ -10946,7 +10952,7 @@
         <v>19</v>
       </c>
       <c r="M32" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N32" s="3">
@@ -10993,7 +10999,7 @@
         <v>25</v>
       </c>
       <c r="M33" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N33" s="3">
@@ -11040,7 +11046,7 @@
         <v>19</v>
       </c>
       <c r="M34" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N34" s="3">
@@ -11087,7 +11093,7 @@
         <v>19</v>
       </c>
       <c r="M35" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N35" s="3">
@@ -11134,7 +11140,7 @@
         <v>183</v>
       </c>
       <c r="M36" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N36" s="3">
@@ -11181,7 +11187,7 @@
         <v>188</v>
       </c>
       <c r="M37" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N37" s="3">
@@ -11228,7 +11234,7 @@
         <v>194</v>
       </c>
       <c r="M38" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N38" s="3">
@@ -11275,7 +11281,7 @@
         <v>19</v>
       </c>
       <c r="M39" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N39" s="3">
@@ -11322,7 +11328,7 @@
         <v>25</v>
       </c>
       <c r="M40" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N40" s="3">
@@ -11369,7 +11375,7 @@
         <v>19</v>
       </c>
       <c r="M41" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N41" s="3">
@@ -11416,7 +11422,7 @@
         <v>25</v>
       </c>
       <c r="M42" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N42" s="3">
@@ -11463,7 +11469,7 @@
         <v>215</v>
       </c>
       <c r="M43" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N43" s="3">
@@ -11510,7 +11516,7 @@
         <v>19</v>
       </c>
       <c r="M44" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N44" s="3">
@@ -11557,7 +11563,7 @@
         <v>19</v>
       </c>
       <c r="M45" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N45" s="3">
@@ -11604,7 +11610,7 @@
         <v>183</v>
       </c>
       <c r="M46" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N46" s="3">
@@ -11651,7 +11657,7 @@
         <v>183</v>
       </c>
       <c r="M47" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N47" s="3">
@@ -11698,7 +11704,7 @@
         <v>19</v>
       </c>
       <c r="M48" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N48" s="3">
@@ -11745,7 +11751,7 @@
         <v>25</v>
       </c>
       <c r="M49" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N49" s="3">
@@ -11792,7 +11798,7 @@
         <v>183</v>
       </c>
       <c r="M50" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N50" s="3">
@@ -11839,7 +11845,7 @@
         <v>19</v>
       </c>
       <c r="M51" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N51" s="3">
@@ -11886,7 +11892,7 @@
         <v>183</v>
       </c>
       <c r="M52" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N52" s="3">
@@ -11933,7 +11939,7 @@
         <v>183</v>
       </c>
       <c r="M53" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N53" s="3">
@@ -11980,7 +11986,7 @@
         <v>19</v>
       </c>
       <c r="M54" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N54" s="3">
@@ -12027,7 +12033,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N55" s="3">
@@ -12074,7 +12080,7 @@
         <v>25</v>
       </c>
       <c r="M56" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N56" s="3">
@@ -12121,7 +12127,7 @@
         <v>25</v>
       </c>
       <c r="M57" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N57" s="3">
@@ -12168,7 +12174,7 @@
         <v>25</v>
       </c>
       <c r="M58" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N58" s="3">
@@ -12215,7 +12221,7 @@
         <v>183</v>
       </c>
       <c r="M59" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N59" s="3">
@@ -12262,7 +12268,7 @@
         <v>19</v>
       </c>
       <c r="M60" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N60" s="3">
@@ -12309,7 +12315,7 @@
         <v>183</v>
       </c>
       <c r="M61" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N61" s="3">
@@ -12356,7 +12362,7 @@
         <v>183</v>
       </c>
       <c r="M62" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N62" s="3">
@@ -12403,7 +12409,7 @@
         <v>19</v>
       </c>
       <c r="M63" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N63" s="3">
@@ -12450,7 +12456,7 @@
         <v>183</v>
       </c>
       <c r="M64" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N64" s="3">
@@ -12497,7 +12503,7 @@
         <v>19</v>
       </c>
       <c r="M65" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N65" s="3">
@@ -12544,7 +12550,7 @@
         <v>19</v>
       </c>
       <c r="M66" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N66" s="3">
@@ -12591,7 +12597,7 @@
         <v>25</v>
       </c>
       <c r="M67" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N67" s="3">
@@ -12638,7 +12644,7 @@
         <v>25</v>
       </c>
       <c r="M68" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N68" s="3">
@@ -12685,7 +12691,7 @@
         <v>19</v>
       </c>
       <c r="M69" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N69" s="3">
@@ -12732,7 +12738,7 @@
         <v>183</v>
       </c>
       <c r="M70" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N70" s="3">
@@ -12779,7 +12785,7 @@
         <v>25</v>
       </c>
       <c r="M71" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N71" s="3">
@@ -12826,7 +12832,7 @@
         <v>25</v>
       </c>
       <c r="M72" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N72" s="3">
@@ -12873,7 +12879,7 @@
         <v>183</v>
       </c>
       <c r="M73" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N73" s="3">
@@ -12920,7 +12926,7 @@
         <v>19</v>
       </c>
       <c r="M74" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N74" s="3">
@@ -12967,7 +12973,7 @@
         <v>19</v>
       </c>
       <c r="M75" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N75" s="3">
@@ -13014,7 +13020,7 @@
         <v>19</v>
       </c>
       <c r="M76" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N76" s="3">
@@ -13061,7 +13067,7 @@
         <v>183</v>
       </c>
       <c r="M77" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N77" s="3">
@@ -13108,7 +13114,7 @@
         <v>19</v>
       </c>
       <c r="M78" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N78" s="3">
@@ -13155,7 +13161,7 @@
         <v>25</v>
       </c>
       <c r="M79" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N79" s="3">
@@ -13202,7 +13208,7 @@
         <v>19</v>
       </c>
       <c r="M80" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N80" s="3">
@@ -13249,7 +13255,7 @@
         <v>25</v>
       </c>
       <c r="M81" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N81" s="3">
@@ -13296,7 +13302,7 @@
         <v>19</v>
       </c>
       <c r="M82" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N82" s="3">
@@ -13343,7 +13349,7 @@
         <v>183</v>
       </c>
       <c r="M83" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N83" s="3">
@@ -13390,7 +13396,7 @@
         <v>19</v>
       </c>
       <c r="M84" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N84" s="3">
@@ -13437,7 +13443,7 @@
         <v>25</v>
       </c>
       <c r="M85" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N85" s="3">
@@ -13484,7 +13490,7 @@
         <v>19</v>
       </c>
       <c r="M86" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N86" s="3">
@@ -13531,7 +13537,7 @@
         <v>25</v>
       </c>
       <c r="M87" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N87" s="3">
@@ -13578,7 +13584,7 @@
         <v>19</v>
       </c>
       <c r="M88" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N88" s="3">
@@ -13625,7 +13631,7 @@
         <v>25</v>
       </c>
       <c r="M89" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N89" s="3">
@@ -13672,7 +13678,7 @@
         <v>19</v>
       </c>
       <c r="M90" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N90" s="3">
@@ -13719,7 +13725,7 @@
         <v>25</v>
       </c>
       <c r="M91" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N91" s="3">
@@ -13766,7 +13772,7 @@
         <v>19</v>
       </c>
       <c r="M92" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N92" s="3">
@@ -13813,7 +13819,7 @@
         <v>183</v>
       </c>
       <c r="M93" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N93" s="3">
@@ -13860,7 +13866,7 @@
         <v>25</v>
       </c>
       <c r="M94" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N94" s="3">
@@ -13907,7 +13913,7 @@
         <v>25</v>
       </c>
       <c r="M95" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N95" s="3">
@@ -13954,7 +13960,7 @@
         <v>19</v>
       </c>
       <c r="M96" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N96" s="3">
@@ -14001,7 +14007,7 @@
         <v>183</v>
       </c>
       <c r="M97" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N97" s="3">
@@ -14048,7 +14054,7 @@
         <v>19</v>
       </c>
       <c r="M98" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N98" s="3">
@@ -14095,7 +14101,7 @@
         <v>25</v>
       </c>
       <c r="M99" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N99" s="3">
@@ -14142,7 +14148,7 @@
         <v>25</v>
       </c>
       <c r="M100" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N100" s="3">
@@ -14189,7 +14195,7 @@
         <v>25</v>
       </c>
       <c r="M101" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N101" s="3">
@@ -14236,7 +14242,7 @@
         <v>25</v>
       </c>
       <c r="M102" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N102" s="3">
@@ -14283,7 +14289,7 @@
         <v>19</v>
       </c>
       <c r="M103" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N103" s="3">
@@ -14330,7 +14336,7 @@
         <v>19</v>
       </c>
       <c r="M104" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N104" s="3">
@@ -14377,7 +14383,7 @@
         <v>19</v>
       </c>
       <c r="M105" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N105" s="3">
@@ -14424,7 +14430,7 @@
         <v>25</v>
       </c>
       <c r="M106" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N106" s="3">
@@ -14471,7 +14477,7 @@
         <v>183</v>
       </c>
       <c r="M107" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N107" s="3">
@@ -14518,7 +14524,7 @@
         <v>19</v>
       </c>
       <c r="M108" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N108" s="3">
@@ -14565,7 +14571,7 @@
         <v>183</v>
       </c>
       <c r="M109" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N109" s="3">
@@ -14612,7 +14618,7 @@
         <v>19</v>
       </c>
       <c r="M110" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N110" s="3">
@@ -14659,7 +14665,7 @@
         <v>183</v>
       </c>
       <c r="M111" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N111" s="3">
@@ -14706,7 +14712,7 @@
         <v>19</v>
       </c>
       <c r="M112" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N112" s="3">
@@ -14753,7 +14759,7 @@
         <v>25</v>
       </c>
       <c r="M113" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N113" s="3">
@@ -14800,7 +14806,7 @@
         <v>19</v>
       </c>
       <c r="M114" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N114" s="3">
@@ -14847,7 +14853,7 @@
         <v>19</v>
       </c>
       <c r="M115" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N115" s="3">
@@ -14894,7 +14900,7 @@
         <v>25</v>
       </c>
       <c r="M116" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N116" s="3">
@@ -14941,7 +14947,7 @@
         <v>19</v>
       </c>
       <c r="M117" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N117" s="3">
@@ -14988,7 +14994,7 @@
         <v>19</v>
       </c>
       <c r="M118" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N118" s="3">
@@ -15035,7 +15041,7 @@
         <v>25</v>
       </c>
       <c r="M119" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N119" s="3">
@@ -15082,7 +15088,7 @@
         <v>183</v>
       </c>
       <c r="M120" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N120" s="3">
@@ -15129,7 +15135,7 @@
         <v>25</v>
       </c>
       <c r="M121" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N121" s="3">
@@ -15176,7 +15182,7 @@
         <v>25</v>
       </c>
       <c r="M122" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N122" s="3">
@@ -15223,7 +15229,7 @@
         <v>19</v>
       </c>
       <c r="M123" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N123" s="3">
@@ -15270,7 +15276,7 @@
         <v>19</v>
       </c>
       <c r="M124" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N124" s="3">
@@ -15317,7 +15323,7 @@
         <v>19</v>
       </c>
       <c r="M125" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N125" s="3">
@@ -15364,7 +15370,7 @@
         <v>19</v>
       </c>
       <c r="M126" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N126" s="3">
@@ -15411,7 +15417,7 @@
         <v>19</v>
       </c>
       <c r="M127" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N127" s="3">
@@ -15458,7 +15464,7 @@
         <v>19</v>
       </c>
       <c r="M128" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N128" s="3">
@@ -15505,7 +15511,7 @@
         <v>19</v>
       </c>
       <c r="M129" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N129" s="3">
@@ -15552,7 +15558,7 @@
         <v>19</v>
       </c>
       <c r="M130" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N130" s="3">
@@ -15599,7 +15605,7 @@
         <v>19</v>
       </c>
       <c r="M131" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N131" s="3">
@@ -15646,7 +15652,7 @@
         <v>25</v>
       </c>
       <c r="M132" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N132" s="3">
@@ -15693,7 +15699,7 @@
         <v>19</v>
       </c>
       <c r="M133" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N133" s="3">
@@ -15740,7 +15746,7 @@
         <v>25</v>
       </c>
       <c r="M134" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N134" s="3">
@@ -15787,7 +15793,7 @@
         <v>19</v>
       </c>
       <c r="M135" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N135" s="3">
@@ -15834,7 +15840,7 @@
         <v>19</v>
       </c>
       <c r="M136" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N136" s="3">
@@ -15881,7 +15887,7 @@
         <v>25</v>
       </c>
       <c r="M137" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N137" s="3">
@@ -15928,7 +15934,7 @@
         <v>183</v>
       </c>
       <c r="M138" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N138" s="3">
@@ -15975,7 +15981,7 @@
         <v>19</v>
       </c>
       <c r="M139" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N139" s="3">
@@ -16022,7 +16028,7 @@
         <v>19</v>
       </c>
       <c r="M140" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N140" s="3">
@@ -16069,7 +16075,7 @@
         <v>19</v>
       </c>
       <c r="M141" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N141" s="3">
@@ -16116,7 +16122,7 @@
         <v>19</v>
       </c>
       <c r="M142" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N142" s="3">
@@ -16163,7 +16169,7 @@
         <v>19</v>
       </c>
       <c r="M143" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N143" s="3">
@@ -16210,7 +16216,7 @@
         <v>25</v>
       </c>
       <c r="M144" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N144" s="3">
@@ -16257,7 +16263,7 @@
         <v>183</v>
       </c>
       <c r="M145" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N145" s="3">
@@ -16304,7 +16310,7 @@
         <v>19</v>
       </c>
       <c r="M146" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N146" s="3">
@@ -16351,7 +16357,7 @@
         <v>25</v>
       </c>
       <c r="M147" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N147" s="3">
@@ -16398,7 +16404,7 @@
         <v>25</v>
       </c>
       <c r="M148" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N148" s="3">
@@ -16445,7 +16451,7 @@
         <v>19</v>
       </c>
       <c r="M149" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N149" s="3">
@@ -16492,7 +16498,7 @@
         <v>25</v>
       </c>
       <c r="M150" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N150" s="3">
@@ -16539,7 +16545,7 @@
         <v>19</v>
       </c>
       <c r="M151" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N151" s="3">
@@ -16586,7 +16592,7 @@
         <v>25</v>
       </c>
       <c r="M152" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N152" s="3">
@@ -16633,7 +16639,7 @@
         <v>19</v>
       </c>
       <c r="M153" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N153" s="3">
@@ -16680,7 +16686,7 @@
         <v>25</v>
       </c>
       <c r="M154" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N154" s="3">
@@ -16727,7 +16733,7 @@
         <v>19</v>
       </c>
       <c r="M155" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N155" s="3">
@@ -16774,7 +16780,7 @@
         <v>19</v>
       </c>
       <c r="M156" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N156" s="3">
@@ -16821,7 +16827,7 @@
         <v>183</v>
       </c>
       <c r="M157" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N157" s="3">
@@ -16868,7 +16874,7 @@
         <v>183</v>
       </c>
       <c r="M158" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N158" s="3">
@@ -16915,7 +16921,7 @@
         <v>19</v>
       </c>
       <c r="M159" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N159" s="3">
@@ -16962,7 +16968,7 @@
         <v>25</v>
       </c>
       <c r="M160" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N160" s="3">
@@ -17009,7 +17015,7 @@
         <v>25</v>
       </c>
       <c r="M161" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N161" s="3">
@@ -17056,7 +17062,7 @@
         <v>183</v>
       </c>
       <c r="M162" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N162" s="3">
@@ -17103,7 +17109,7 @@
         <v>25</v>
       </c>
       <c r="M163" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N163" s="3">
@@ -17150,7 +17156,7 @@
         <v>19</v>
       </c>
       <c r="M164" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N164" s="3">
@@ -17197,7 +17203,7 @@
         <v>19</v>
       </c>
       <c r="M165" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N165" s="3">
@@ -17244,7 +17250,7 @@
         <v>183</v>
       </c>
       <c r="M166" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N166" s="3">
@@ -17291,7 +17297,7 @@
         <v>19</v>
       </c>
       <c r="M167" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N167" s="3">
@@ -17338,7 +17344,7 @@
         <v>19</v>
       </c>
       <c r="M168" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N168" s="3">
@@ -17385,7 +17391,7 @@
         <v>183</v>
       </c>
       <c r="M169" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N169" s="3">
@@ -17432,7 +17438,7 @@
         <v>19</v>
       </c>
       <c r="M170" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N170" s="3">
@@ -17479,7 +17485,7 @@
         <v>19</v>
       </c>
       <c r="M171" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N171" s="3">
@@ -17526,7 +17532,7 @@
         <v>25</v>
       </c>
       <c r="M172" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N172" s="3">
@@ -17573,7 +17579,7 @@
         <v>25</v>
       </c>
       <c r="M173" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N173" s="3">
@@ -17620,7 +17626,7 @@
         <v>25</v>
       </c>
       <c r="M174" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N174" s="3">
@@ -17667,7 +17673,7 @@
         <v>25</v>
       </c>
       <c r="M175" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N175" s="3">
@@ -17714,7 +17720,7 @@
         <v>25</v>
       </c>
       <c r="M176" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N176" s="3">
@@ -17761,7 +17767,7 @@
         <v>19</v>
       </c>
       <c r="M177" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N177" s="3">
@@ -17808,7 +17814,7 @@
         <v>25</v>
       </c>
       <c r="M178" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N178" s="3">
@@ -17855,7 +17861,7 @@
         <v>183</v>
       </c>
       <c r="M179" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N179" s="3">
@@ -17902,7 +17908,7 @@
         <v>183</v>
       </c>
       <c r="M180" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N180" s="3">
@@ -17949,7 +17955,7 @@
         <v>25</v>
       </c>
       <c r="M181" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N181" s="3">
@@ -17996,7 +18002,7 @@
         <v>25</v>
       </c>
       <c r="M182" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N182" s="3">
@@ -18043,7 +18049,7 @@
         <v>25</v>
       </c>
       <c r="M183" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N183" s="3">
@@ -18090,7 +18096,7 @@
         <v>25</v>
       </c>
       <c r="M184" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N184" s="3">
@@ -18137,7 +18143,7 @@
         <v>25</v>
       </c>
       <c r="M185" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N185" s="3">
@@ -18184,7 +18190,7 @@
         <v>19</v>
       </c>
       <c r="M186" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N186" s="3">
@@ -18231,7 +18237,7 @@
         <v>19</v>
       </c>
       <c r="M187" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N187" s="3">
@@ -18278,7 +18284,7 @@
         <v>19</v>
       </c>
       <c r="M188" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N188" s="3">
@@ -18325,7 +18331,7 @@
         <v>183</v>
       </c>
       <c r="M189" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N189" s="3">
@@ -18372,7 +18378,7 @@
         <v>183</v>
       </c>
       <c r="M190" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N190" s="3">
@@ -18419,7 +18425,7 @@
         <v>19</v>
       </c>
       <c r="M191" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N191" s="3">
@@ -18466,7 +18472,7 @@
         <v>19</v>
       </c>
       <c r="M192" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N192" s="3">
@@ -18513,7 +18519,7 @@
         <v>19</v>
       </c>
       <c r="M193" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N193" s="3">
@@ -18560,7 +18566,7 @@
         <v>19</v>
       </c>
       <c r="M194" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N194" s="3">
@@ -18607,7 +18613,7 @@
         <v>25</v>
       </c>
       <c r="M195" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N195" s="3">
@@ -18654,7 +18660,7 @@
         <v>25</v>
       </c>
       <c r="M196" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N196" s="3">
@@ -18701,7 +18707,7 @@
         <v>19</v>
       </c>
       <c r="M197" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N197" s="3">
@@ -18748,7 +18754,7 @@
         <v>19</v>
       </c>
       <c r="M198" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N198" s="3">
@@ -18795,7 +18801,7 @@
         <v>25</v>
       </c>
       <c r="M199" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N199" s="3">
@@ -18842,7 +18848,7 @@
         <v>19</v>
       </c>
       <c r="M200" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N200" s="3">
@@ -18889,7 +18895,7 @@
         <v>183</v>
       </c>
       <c r="M201" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N201" s="3">
@@ -18936,7 +18942,7 @@
         <v>19</v>
       </c>
       <c r="M202" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N202" s="3">
@@ -18983,7 +18989,7 @@
         <v>19</v>
       </c>
       <c r="M203" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N203" s="3">
@@ -19030,7 +19036,7 @@
         <v>25</v>
       </c>
       <c r="M204" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N204" s="3">
@@ -19077,7 +19083,7 @@
         <v>183</v>
       </c>
       <c r="M205" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N205" s="3">
@@ -19124,7 +19130,7 @@
         <v>183</v>
       </c>
       <c r="M206" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N206" s="3">
@@ -19171,7 +19177,7 @@
         <v>183</v>
       </c>
       <c r="M207" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N207" s="3">
@@ -19218,7 +19224,7 @@
         <v>19</v>
       </c>
       <c r="M208" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N208" s="3">
@@ -19265,7 +19271,7 @@
         <v>19</v>
       </c>
       <c r="M209" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N209" s="3">
@@ -19312,7 +19318,7 @@
         <v>183</v>
       </c>
       <c r="M210" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N210" s="3">
@@ -19359,7 +19365,7 @@
         <v>25</v>
       </c>
       <c r="M211" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N211" s="3">
@@ -19406,7 +19412,7 @@
         <v>25</v>
       </c>
       <c r="M212" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N212" s="3">
@@ -19453,7 +19459,7 @@
         <v>19</v>
       </c>
       <c r="M213" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N213" s="3">
@@ -19500,7 +19506,7 @@
         <v>25</v>
       </c>
       <c r="M214" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N214" s="3">
@@ -19547,7 +19553,7 @@
         <v>19</v>
       </c>
       <c r="M215" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N215" s="3">
@@ -19594,7 +19600,7 @@
         <v>19</v>
       </c>
       <c r="M216" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N216" s="3">
@@ -19641,7 +19647,7 @@
         <v>19</v>
       </c>
       <c r="M217" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N217" s="3">
@@ -19688,7 +19694,7 @@
         <v>19</v>
       </c>
       <c r="M218" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N218" s="3">
@@ -19735,7 +19741,7 @@
         <v>19</v>
       </c>
       <c r="M219" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N219" s="3">
@@ -19782,7 +19788,7 @@
         <v>933</v>
       </c>
       <c r="M220" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N220" s="3">
@@ -19829,7 +19835,7 @@
         <v>19</v>
       </c>
       <c r="M221" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N221" s="3">
@@ -19876,7 +19882,7 @@
         <v>183</v>
       </c>
       <c r="M222" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N222" s="3">
@@ -19923,7 +19929,7 @@
         <v>25</v>
       </c>
       <c r="M223" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N223" s="3">
@@ -19970,7 +19976,7 @@
         <v>183</v>
       </c>
       <c r="M224" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N224" s="3">
@@ -20017,7 +20023,7 @@
         <v>19</v>
       </c>
       <c r="M225" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N225" s="3">
@@ -20064,7 +20070,7 @@
         <v>25</v>
       </c>
       <c r="M226" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N226" s="3">
@@ -20111,7 +20117,7 @@
         <v>19</v>
       </c>
       <c r="M227" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N227" s="3">
@@ -20158,7 +20164,7 @@
         <v>25</v>
       </c>
       <c r="M228" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N228" s="3">
@@ -20205,7 +20211,7 @@
         <v>183</v>
       </c>
       <c r="M229" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N229" s="3">
@@ -20252,7 +20258,7 @@
         <v>25</v>
       </c>
       <c r="M230" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N230" s="3">
@@ -20299,7 +20305,7 @@
         <v>25</v>
       </c>
       <c r="M231" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N231" s="3">
@@ -20346,7 +20352,7 @@
         <v>183</v>
       </c>
       <c r="M232" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N232" s="3">
@@ -20393,7 +20399,7 @@
         <v>19</v>
       </c>
       <c r="M233" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N233" s="3">
@@ -20440,7 +20446,7 @@
         <v>19</v>
       </c>
       <c r="M234" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N234" s="3">
@@ -20487,7 +20493,7 @@
         <v>19</v>
       </c>
       <c r="M235" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N235" s="3">
@@ -20534,7 +20540,7 @@
         <v>183</v>
       </c>
       <c r="M236" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N236" s="3">
@@ -20581,7 +20587,7 @@
         <v>19</v>
       </c>
       <c r="M237" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N237" s="3">
@@ -20628,7 +20634,7 @@
         <v>19</v>
       </c>
       <c r="M238" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N238" s="3">
@@ -20675,7 +20681,7 @@
         <v>25</v>
       </c>
       <c r="M239" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N239" s="3">
@@ -20722,7 +20728,7 @@
         <v>25</v>
       </c>
       <c r="M240" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N240" s="3">
@@ -20769,7 +20775,7 @@
         <v>19</v>
       </c>
       <c r="M241" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N241" s="3">
@@ -20816,7 +20822,7 @@
         <v>19</v>
       </c>
       <c r="M242" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N242" s="3">
@@ -20863,7 +20869,7 @@
         <v>183</v>
       </c>
       <c r="M243" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N243" s="3">
@@ -20910,7 +20916,7 @@
         <v>25</v>
       </c>
       <c r="M244" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N244" s="3">
@@ -20957,7 +20963,7 @@
         <v>25</v>
       </c>
       <c r="M245" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N245" s="3">
@@ -21004,7 +21010,7 @@
         <v>19</v>
       </c>
       <c r="M246" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N246" s="3">
@@ -21051,7 +21057,7 @@
         <v>183</v>
       </c>
       <c r="M247" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N247" s="3">
@@ -21098,7 +21104,7 @@
         <v>19</v>
       </c>
       <c r="M248" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N248" s="3">
@@ -21145,7 +21151,7 @@
         <v>19</v>
       </c>
       <c r="M249" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N249" s="3">
@@ -21192,7 +21198,7 @@
         <v>19</v>
       </c>
       <c r="M250" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N250" s="3">
@@ -21239,7 +21245,7 @@
         <v>19</v>
       </c>
       <c r="M251" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N251" s="3">
@@ -21286,7 +21292,7 @@
         <v>25</v>
       </c>
       <c r="M252" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N252" s="3">
@@ -21333,7 +21339,7 @@
         <v>25</v>
       </c>
       <c r="M253" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N253" s="3">
@@ -21380,7 +21386,7 @@
         <v>25</v>
       </c>
       <c r="M254" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N254" s="3">
@@ -21427,7 +21433,7 @@
         <v>25</v>
       </c>
       <c r="M255" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N255" s="3">
@@ -21474,7 +21480,7 @@
         <v>19</v>
       </c>
       <c r="M256" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N256" s="3">
@@ -21521,7 +21527,7 @@
         <v>25</v>
       </c>
       <c r="M257" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N257" s="3">
@@ -21568,7 +21574,7 @@
         <v>25</v>
       </c>
       <c r="M258" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N258" s="3">
@@ -21615,7 +21621,7 @@
         <v>25</v>
       </c>
       <c r="M259" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N259" s="3">
@@ -21662,7 +21668,7 @@
         <v>25</v>
       </c>
       <c r="M260" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N260" s="3">
@@ -21709,7 +21715,7 @@
         <v>25</v>
       </c>
       <c r="M261" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N261" s="3">
@@ -21756,7 +21762,7 @@
         <v>19</v>
       </c>
       <c r="M262" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N262" s="3">
@@ -21803,7 +21809,7 @@
         <v>25</v>
       </c>
       <c r="M263" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N263" s="3">
@@ -21850,7 +21856,7 @@
         <v>183</v>
       </c>
       <c r="M264" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N264" s="3">
@@ -21897,7 +21903,7 @@
         <v>183</v>
       </c>
       <c r="M265" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N265" s="3">
@@ -21944,7 +21950,7 @@
         <v>19</v>
       </c>
       <c r="M266" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N266" s="3">
@@ -21991,7 +21997,7 @@
         <v>19</v>
       </c>
       <c r="M267" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N267" s="3">
@@ -22038,7 +22044,7 @@
         <v>25</v>
       </c>
       <c r="M268" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N268" s="3">
@@ -22085,7 +22091,7 @@
         <v>19</v>
       </c>
       <c r="M269" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N269" s="3">
@@ -22132,7 +22138,7 @@
         <v>25</v>
       </c>
       <c r="M270" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N270" s="3">
@@ -22179,7 +22185,7 @@
         <v>183</v>
       </c>
       <c r="M271" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N271" s="3">
@@ -22226,7 +22232,7 @@
         <v>25</v>
       </c>
       <c r="M272" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N272" s="3">
@@ -22273,7 +22279,7 @@
         <v>19</v>
       </c>
       <c r="M273" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N273" s="3">
@@ -22320,7 +22326,7 @@
         <v>1149</v>
       </c>
       <c r="M274" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N274" s="3">
@@ -22367,7 +22373,7 @@
         <v>19</v>
       </c>
       <c r="M275" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N275" s="3">
@@ -22414,7 +22420,7 @@
         <v>183</v>
       </c>
       <c r="M276" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N276" s="3">
@@ -22461,7 +22467,7 @@
         <v>19</v>
       </c>
       <c r="M277" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N277" s="3">
@@ -22508,7 +22514,7 @@
         <v>183</v>
       </c>
       <c r="M278" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N278" s="3">
@@ -22555,7 +22561,7 @@
         <v>25</v>
       </c>
       <c r="M279" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N279" s="3">
@@ -22602,7 +22608,7 @@
         <v>183</v>
       </c>
       <c r="M280" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N280" s="3">
@@ -22649,7 +22655,7 @@
         <v>25</v>
       </c>
       <c r="M281" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N281" s="3">
@@ -22696,7 +22702,7 @@
         <v>25</v>
       </c>
       <c r="M282" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N282" s="3">
@@ -22743,7 +22749,7 @@
         <v>183</v>
       </c>
       <c r="M283" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N283" s="3">
@@ -22790,7 +22796,7 @@
         <v>25</v>
       </c>
       <c r="M284" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N284" s="3">
@@ -22837,7 +22843,7 @@
         <v>19</v>
       </c>
       <c r="M285" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N285" s="3">
@@ -22884,7 +22890,7 @@
         <v>25</v>
       </c>
       <c r="M286" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N286" s="3">
@@ -22931,7 +22937,7 @@
         <v>25</v>
       </c>
       <c r="M287" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N287" s="3">
@@ -22978,7 +22984,7 @@
         <v>25</v>
       </c>
       <c r="M288" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N288" s="3">
@@ -23025,7 +23031,7 @@
         <v>19</v>
       </c>
       <c r="M289" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N289" s="3">
@@ -23072,7 +23078,7 @@
         <v>25</v>
       </c>
       <c r="M290" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N290" s="3">
@@ -23119,7 +23125,7 @@
         <v>19</v>
       </c>
       <c r="M291" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N291" s="3">
@@ -23166,7 +23172,7 @@
         <v>19</v>
       </c>
       <c r="M292" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N292" s="3">
@@ -23213,7 +23219,7 @@
         <v>25</v>
       </c>
       <c r="M293" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N293" s="3">
@@ -23260,7 +23266,7 @@
         <v>183</v>
       </c>
       <c r="M294" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N294" s="3">
@@ -23307,7 +23313,7 @@
         <v>25</v>
       </c>
       <c r="M295" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N295" s="3">
@@ -23354,7 +23360,7 @@
         <v>25</v>
       </c>
       <c r="M296" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N296" s="3">
@@ -23401,7 +23407,7 @@
         <v>19</v>
       </c>
       <c r="M297" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N297" s="3">
@@ -23448,7 +23454,7 @@
         <v>183</v>
       </c>
       <c r="M298" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N298" s="3">
@@ -23495,7 +23501,7 @@
         <v>25</v>
       </c>
       <c r="M299" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N299" s="3">
@@ -23542,7 +23548,7 @@
         <v>19</v>
       </c>
       <c r="M300" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N300" s="3">
@@ -23589,7 +23595,7 @@
         <v>19</v>
       </c>
       <c r="M301" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N301" s="3">
@@ -23636,7 +23642,7 @@
         <v>19</v>
       </c>
       <c r="M302" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N302" s="3">
@@ -23683,7 +23689,7 @@
         <v>19</v>
       </c>
       <c r="M303" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N303" s="3">
@@ -23730,7 +23736,7 @@
         <v>25</v>
       </c>
       <c r="M304" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N304" s="3">
@@ -23777,7 +23783,7 @@
         <v>19</v>
       </c>
       <c r="M305" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N305" s="3">
@@ -23824,7 +23830,7 @@
         <v>19</v>
       </c>
       <c r="M306" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N306" s="3">
@@ -23871,7 +23877,7 @@
         <v>25</v>
       </c>
       <c r="M307" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N307" s="3">
@@ -23918,7 +23924,7 @@
         <v>19</v>
       </c>
       <c r="M308" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N308" s="3">
@@ -23965,7 +23971,7 @@
         <v>183</v>
       </c>
       <c r="M309" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N309" s="3">
@@ -24012,7 +24018,7 @@
         <v>183</v>
       </c>
       <c r="M310" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N310" s="3">
@@ -24059,7 +24065,7 @@
         <v>19</v>
       </c>
       <c r="M311" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N311" s="3">
@@ -24106,7 +24112,7 @@
         <v>19</v>
       </c>
       <c r="M312" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N312" s="3">
@@ -24153,7 +24159,7 @@
         <v>183</v>
       </c>
       <c r="M313" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N313" s="3">
@@ -24200,7 +24206,7 @@
         <v>19</v>
       </c>
       <c r="M314" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N314" s="3">
@@ -24247,7 +24253,7 @@
         <v>19</v>
       </c>
       <c r="M315" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N315" s="3">
@@ -24294,7 +24300,7 @@
         <v>25</v>
       </c>
       <c r="M316" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N316" s="3">
@@ -24341,7 +24347,7 @@
         <v>19</v>
       </c>
       <c r="M317" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N317" s="3">
@@ -24388,7 +24394,7 @@
         <v>25</v>
       </c>
       <c r="M318" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N318" s="3">
@@ -24435,7 +24441,7 @@
         <v>25</v>
       </c>
       <c r="M319" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N319" s="3">
@@ -24482,7 +24488,7 @@
         <v>25</v>
       </c>
       <c r="M320" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N320" s="3">
@@ -24529,7 +24535,7 @@
         <v>25</v>
       </c>
       <c r="M321" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N321" s="3">
@@ -24576,7 +24582,7 @@
         <v>25</v>
       </c>
       <c r="M322" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N322" s="3">
@@ -24623,7 +24629,7 @@
         <v>19</v>
       </c>
       <c r="M323" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N323" s="3">
@@ -24670,7 +24676,7 @@
         <v>19</v>
       </c>
       <c r="M324" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N324" s="3">
@@ -24717,7 +24723,7 @@
         <v>183</v>
       </c>
       <c r="M325" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N325" s="3">
@@ -24764,7 +24770,7 @@
         <v>19</v>
       </c>
       <c r="M326" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N326" s="3">
@@ -24811,7 +24817,7 @@
         <v>25</v>
       </c>
       <c r="M327" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N327" s="3">
@@ -24858,7 +24864,7 @@
         <v>19</v>
       </c>
       <c r="M328" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N328" s="3">
@@ -24905,7 +24911,7 @@
         <v>25</v>
       </c>
       <c r="M329" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N329" s="3">
@@ -24952,7 +24958,7 @@
         <v>183</v>
       </c>
       <c r="M330" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N330" s="3">
@@ -24999,7 +25005,7 @@
         <v>25</v>
       </c>
       <c r="M331" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N331" s="3">
@@ -25046,7 +25052,7 @@
         <v>19</v>
       </c>
       <c r="M332" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N332" s="3">
@@ -25093,7 +25099,7 @@
         <v>25</v>
       </c>
       <c r="M333" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N333" s="3">
@@ -25140,7 +25146,7 @@
         <v>25</v>
       </c>
       <c r="M334" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N334" s="3">
@@ -25187,7 +25193,7 @@
         <v>25</v>
       </c>
       <c r="M335" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N335" s="3">
@@ -25234,7 +25240,7 @@
         <v>19</v>
       </c>
       <c r="M336" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N336" s="3">
@@ -25281,7 +25287,7 @@
         <v>25</v>
       </c>
       <c r="M337" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N337" s="3">
@@ -25328,7 +25334,7 @@
         <v>19</v>
       </c>
       <c r="M338" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N338" s="3">
@@ -25375,7 +25381,7 @@
         <v>19</v>
       </c>
       <c r="M339" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N339" s="3">
@@ -25422,7 +25428,7 @@
         <v>19</v>
       </c>
       <c r="M340" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N340" s="3">
@@ -25469,7 +25475,7 @@
         <v>183</v>
       </c>
       <c r="M341" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N341" s="3">
@@ -25516,7 +25522,7 @@
         <v>25</v>
       </c>
       <c r="M342" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N342" s="3">
@@ -25563,7 +25569,7 @@
         <v>19</v>
       </c>
       <c r="M343" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N343" s="3">
@@ -25610,7 +25616,7 @@
         <v>25</v>
       </c>
       <c r="M344" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N344" s="3">
@@ -25657,7 +25663,7 @@
         <v>19</v>
       </c>
       <c r="M345" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N345" s="3">
@@ -25704,7 +25710,7 @@
         <v>19</v>
       </c>
       <c r="M346" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N346" s="3">
@@ -25751,7 +25757,7 @@
         <v>183</v>
       </c>
       <c r="M347" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N347" s="3">
@@ -25798,7 +25804,7 @@
         <v>19</v>
       </c>
       <c r="M348" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N348" s="3">
@@ -25845,7 +25851,7 @@
         <v>19</v>
       </c>
       <c r="M349" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N349" s="3">
@@ -25892,7 +25898,7 @@
         <v>25</v>
       </c>
       <c r="M350" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N350" s="3">
@@ -25939,7 +25945,7 @@
         <v>19</v>
       </c>
       <c r="M351" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N351" s="3">
@@ -25986,7 +25992,7 @@
         <v>25</v>
       </c>
       <c r="M352" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N352" s="3">
@@ -26033,7 +26039,7 @@
         <v>19</v>
       </c>
       <c r="M353" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N353" s="3">
@@ -26080,7 +26086,7 @@
         <v>183</v>
       </c>
       <c r="M354" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N354" s="3">
@@ -26127,7 +26133,7 @@
         <v>25</v>
       </c>
       <c r="M355" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N355" s="3">
@@ -26174,7 +26180,7 @@
         <v>19</v>
       </c>
       <c r="M356" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N356" s="3">
@@ -26221,7 +26227,7 @@
         <v>19</v>
       </c>
       <c r="M357" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N357" s="3">
@@ -26268,7 +26274,7 @@
         <v>25</v>
       </c>
       <c r="M358" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N358" s="3">
@@ -26315,7 +26321,7 @@
         <v>19</v>
       </c>
       <c r="M359" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N359" s="3">
@@ -26362,7 +26368,7 @@
         <v>19</v>
       </c>
       <c r="M360" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N360" s="3">
@@ -26409,7 +26415,7 @@
         <v>19</v>
       </c>
       <c r="M361" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N361" s="3">
@@ -26456,7 +26462,7 @@
         <v>183</v>
       </c>
       <c r="M362" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N362" s="3">
@@ -26503,7 +26509,7 @@
         <v>25</v>
       </c>
       <c r="M363" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N363" s="3">
@@ -26550,7 +26556,7 @@
         <v>19</v>
       </c>
       <c r="M364" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N364" s="3">
@@ -26597,7 +26603,7 @@
         <v>19</v>
       </c>
       <c r="M365" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N365" s="3">
@@ -26644,7 +26650,7 @@
         <v>25</v>
       </c>
       <c r="M366" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N366" s="3">
@@ -26691,7 +26697,7 @@
         <v>19</v>
       </c>
       <c r="M367" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N367" s="3">
@@ -26738,7 +26744,7 @@
         <v>19</v>
       </c>
       <c r="M368" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N368" s="3">
@@ -26785,7 +26791,7 @@
         <v>25</v>
       </c>
       <c r="M369" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N369" s="3">
@@ -26832,7 +26838,7 @@
         <v>19</v>
       </c>
       <c r="M370" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N370" s="3">
@@ -26879,7 +26885,7 @@
         <v>183</v>
       </c>
       <c r="M371" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N371" s="3">
@@ -26926,7 +26932,7 @@
         <v>19</v>
       </c>
       <c r="M372" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N372" s="3">
@@ -26973,7 +26979,7 @@
         <v>19</v>
       </c>
       <c r="M373" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N373" s="3">
@@ -27020,7 +27026,7 @@
         <v>19</v>
       </c>
       <c r="M374" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N374" s="3">
@@ -27067,7 +27073,7 @@
         <v>19</v>
       </c>
       <c r="M375" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N375" s="3">
@@ -27114,7 +27120,7 @@
         <v>1556</v>
       </c>
       <c r="M376" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N376" s="3">
@@ -27161,7 +27167,7 @@
         <v>19</v>
       </c>
       <c r="M377" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N377" s="3">
@@ -27208,7 +27214,7 @@
         <v>19</v>
       </c>
       <c r="M378" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N378" s="3">
@@ -27255,7 +27261,7 @@
         <v>183</v>
       </c>
       <c r="M379" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N379" s="3">
@@ -27302,7 +27308,7 @@
         <v>25</v>
       </c>
       <c r="M380" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N380" s="3">
@@ -27349,7 +27355,7 @@
         <v>25</v>
       </c>
       <c r="M381" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N381" s="3">
@@ -27396,7 +27402,7 @@
         <v>19</v>
       </c>
       <c r="M382" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N382" s="3">
@@ -27443,7 +27449,7 @@
         <v>19</v>
       </c>
       <c r="M383" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N383" s="3">
@@ -27490,7 +27496,7 @@
         <v>25</v>
       </c>
       <c r="M384" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N384" s="3">
@@ -27537,7 +27543,7 @@
         <v>183</v>
       </c>
       <c r="M385" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N385" s="3">
@@ -27584,7 +27590,7 @@
         <v>19</v>
       </c>
       <c r="M386" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N386" s="3">
@@ -27631,7 +27637,7 @@
         <v>19</v>
       </c>
       <c r="M387" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N387" s="3">
@@ -27678,7 +27684,7 @@
         <v>19</v>
       </c>
       <c r="M388" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N388" s="3">
@@ -27725,7 +27731,7 @@
         <v>25</v>
       </c>
       <c r="M389" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N389" s="3">
@@ -27772,7 +27778,7 @@
         <v>25</v>
       </c>
       <c r="M390" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N390" s="3">
@@ -27819,7 +27825,7 @@
         <v>19</v>
       </c>
       <c r="M391" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N391" s="3">
@@ -27866,7 +27872,7 @@
         <v>25</v>
       </c>
       <c r="M392" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N392" s="3">
@@ -27913,7 +27919,7 @@
         <v>183</v>
       </c>
       <c r="M393" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N393" s="3">
@@ -27960,7 +27966,7 @@
         <v>19</v>
       </c>
       <c r="M394" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N394" s="3">
@@ -28007,7 +28013,7 @@
         <v>183</v>
       </c>
       <c r="M395" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N395" s="3">
@@ -28054,7 +28060,7 @@
         <v>19</v>
       </c>
       <c r="M396" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N396" s="3">
@@ -28101,7 +28107,7 @@
         <v>25</v>
       </c>
       <c r="M397" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N397" s="3">
@@ -28148,7 +28154,7 @@
         <v>19</v>
       </c>
       <c r="M398" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N398" s="3">
@@ -28195,7 +28201,7 @@
         <v>183</v>
       </c>
       <c r="M399" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N399" s="3">
@@ -28242,7 +28248,7 @@
         <v>25</v>
       </c>
       <c r="M400" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N400" s="3">
@@ -28289,7 +28295,7 @@
         <v>19</v>
       </c>
       <c r="M401" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N401" s="3">
@@ -28336,7 +28342,7 @@
         <v>25</v>
       </c>
       <c r="M402" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N402" s="3">
@@ -28383,7 +28389,7 @@
         <v>183</v>
       </c>
       <c r="M403" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N403" s="3">
@@ -28430,7 +28436,7 @@
         <v>25</v>
       </c>
       <c r="M404" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N404" s="3">
@@ -28477,7 +28483,7 @@
         <v>19</v>
       </c>
       <c r="M405" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N405" s="3">
@@ -28524,7 +28530,7 @@
         <v>19</v>
       </c>
       <c r="M406" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N406" s="3">
@@ -28571,7 +28577,7 @@
         <v>183</v>
       </c>
       <c r="M407" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N407" s="3">
@@ -28618,7 +28624,7 @@
         <v>25</v>
       </c>
       <c r="M408" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N408" s="3">
@@ -28665,7 +28671,7 @@
         <v>19</v>
       </c>
       <c r="M409" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N409" s="3">
@@ -28712,7 +28718,7 @@
         <v>183</v>
       </c>
       <c r="M410" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N410" s="3">
@@ -28759,7 +28765,7 @@
         <v>19</v>
       </c>
       <c r="M411" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N411" s="3">
@@ -28806,7 +28812,7 @@
         <v>25</v>
       </c>
       <c r="M412" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N412" s="3">
@@ -28853,7 +28859,7 @@
         <v>183</v>
       </c>
       <c r="M413" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N413" s="3">
@@ -28900,7 +28906,7 @@
         <v>19</v>
       </c>
       <c r="M414" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N414" s="3">
@@ -28947,7 +28953,7 @@
         <v>25</v>
       </c>
       <c r="M415" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N415" s="3">
@@ -28994,7 +29000,7 @@
         <v>183</v>
       </c>
       <c r="M416" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N416" s="3">
@@ -29041,7 +29047,7 @@
         <v>25</v>
       </c>
       <c r="M417" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N417" s="3">
@@ -29088,7 +29094,7 @@
         <v>19</v>
       </c>
       <c r="M418" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N418" s="3">
@@ -29135,7 +29141,7 @@
         <v>25</v>
       </c>
       <c r="M419" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N419" s="3">
@@ -29182,7 +29188,7 @@
         <v>25</v>
       </c>
       <c r="M420" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N420" s="3">
@@ -29229,7 +29235,7 @@
         <v>25</v>
       </c>
       <c r="M421" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N421" s="3">
@@ -29276,7 +29282,7 @@
         <v>19</v>
       </c>
       <c r="M422" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N422" s="3">
@@ -29323,7 +29329,7 @@
         <v>25</v>
       </c>
       <c r="M423" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N423" s="3">
@@ -29370,7 +29376,7 @@
         <v>19</v>
       </c>
       <c r="M424" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N424" s="3">
@@ -29417,7 +29423,7 @@
         <v>19</v>
       </c>
       <c r="M425" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N425" s="3">
@@ -29464,7 +29470,7 @@
         <v>183</v>
       </c>
       <c r="M426" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N426" s="3">
@@ -29511,7 +29517,7 @@
         <v>19</v>
       </c>
       <c r="M427" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N427" s="3">
@@ -29558,7 +29564,7 @@
         <v>19</v>
       </c>
       <c r="M428" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N428" s="3">
@@ -29605,7 +29611,7 @@
         <v>19</v>
       </c>
       <c r="M429" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N429" s="3">
@@ -29652,7 +29658,7 @@
         <v>19</v>
       </c>
       <c r="M430" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N430" s="3">
@@ -29699,7 +29705,7 @@
         <v>19</v>
       </c>
       <c r="M431" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N431" s="3">
@@ -29746,7 +29752,7 @@
         <v>25</v>
       </c>
       <c r="M432" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N432" s="3">
@@ -29793,7 +29799,7 @@
         <v>19</v>
       </c>
       <c r="M433" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N433" s="3">
@@ -29840,7 +29846,7 @@
         <v>183</v>
       </c>
       <c r="M434" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N434" s="3">
@@ -29887,7 +29893,7 @@
         <v>19</v>
       </c>
       <c r="M435" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N435" s="3">
@@ -29934,7 +29940,7 @@
         <v>25</v>
       </c>
       <c r="M436" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N436" s="3">
@@ -29981,7 +29987,7 @@
         <v>183</v>
       </c>
       <c r="M437" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N437" s="3">
@@ -30028,7 +30034,7 @@
         <v>25</v>
       </c>
       <c r="M438" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N438" s="3">
@@ -30075,7 +30081,7 @@
         <v>19</v>
       </c>
       <c r="M439" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N439" s="3">
@@ -30122,7 +30128,7 @@
         <v>25</v>
       </c>
       <c r="M440" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N440" s="3">
@@ -30169,7 +30175,7 @@
         <v>19</v>
       </c>
       <c r="M441" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N441" s="3">
@@ -30216,7 +30222,7 @@
         <v>25</v>
       </c>
       <c r="M442" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N442" s="3">
@@ -30263,7 +30269,7 @@
         <v>25</v>
       </c>
       <c r="M443" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N443" s="3">
@@ -30310,7 +30316,7 @@
         <v>19</v>
       </c>
       <c r="M444" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N444" s="3">
@@ -30357,7 +30363,7 @@
         <v>25</v>
       </c>
       <c r="M445" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N445" s="3">
@@ -30404,7 +30410,7 @@
         <v>25</v>
       </c>
       <c r="M446" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N446" s="3">
@@ -30451,7 +30457,7 @@
         <v>25</v>
       </c>
       <c r="M447" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N447" s="3">
@@ -30498,7 +30504,7 @@
         <v>19</v>
       </c>
       <c r="M448" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N448" s="3">
@@ -30545,7 +30551,7 @@
         <v>25</v>
       </c>
       <c r="M449" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N449" s="3">
@@ -30592,7 +30598,7 @@
         <v>19</v>
       </c>
       <c r="M450" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N450" s="3">
@@ -30639,7 +30645,7 @@
         <v>183</v>
       </c>
       <c r="M451" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N451" s="3">
@@ -30686,7 +30692,7 @@
         <v>25</v>
       </c>
       <c r="M452" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N452" s="3">
@@ -30733,7 +30739,7 @@
         <v>19</v>
       </c>
       <c r="M453" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N453" s="3">
@@ -30780,7 +30786,7 @@
         <v>19</v>
       </c>
       <c r="M454" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N454" s="3">
@@ -30827,7 +30833,7 @@
         <v>25</v>
       </c>
       <c r="M455" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N455" s="3">
@@ -30874,7 +30880,7 @@
         <v>183</v>
       </c>
       <c r="M456" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N456" s="3">
@@ -30921,7 +30927,7 @@
         <v>19</v>
       </c>
       <c r="M457" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N457" s="3">
@@ -30968,7 +30974,7 @@
         <v>25</v>
       </c>
       <c r="M458" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N458" s="3">
@@ -31015,7 +31021,7 @@
         <v>19</v>
       </c>
       <c r="M459" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N459" s="3">
@@ -31062,7 +31068,7 @@
         <v>19</v>
       </c>
       <c r="M460" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N460" s="3">
@@ -31109,7 +31115,7 @@
         <v>19</v>
       </c>
       <c r="M461" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N461" s="3">
@@ -31156,7 +31162,7 @@
         <v>183</v>
       </c>
       <c r="M462" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N462" s="3">
@@ -31203,7 +31209,7 @@
         <v>25</v>
       </c>
       <c r="M463" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N463" s="3">
@@ -31250,7 +31256,7 @@
         <v>183</v>
       </c>
       <c r="M464" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N464" s="3">
@@ -31297,7 +31303,7 @@
         <v>25</v>
       </c>
       <c r="M465" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N465" s="3">
@@ -31344,7 +31350,7 @@
         <v>25</v>
       </c>
       <c r="M466" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N466" s="3">
@@ -31391,7 +31397,7 @@
         <v>25</v>
       </c>
       <c r="M467" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N467" s="3">
@@ -31438,7 +31444,7 @@
         <v>25</v>
       </c>
       <c r="M468" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N468" s="3">
@@ -31485,7 +31491,7 @@
         <v>25</v>
       </c>
       <c r="M469" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N469" s="3">
@@ -31532,7 +31538,7 @@
         <v>19</v>
       </c>
       <c r="M470" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N470" s="3">
@@ -31579,7 +31585,7 @@
         <v>19</v>
       </c>
       <c r="M471" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N471" s="3">
@@ -31626,7 +31632,7 @@
         <v>25</v>
       </c>
       <c r="M472" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N472" s="3">
@@ -31673,7 +31679,7 @@
         <v>183</v>
       </c>
       <c r="M473" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N473" s="3">
@@ -31720,7 +31726,7 @@
         <v>19</v>
       </c>
       <c r="M474" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N474" s="3">
@@ -31767,7 +31773,7 @@
         <v>19</v>
       </c>
       <c r="M475" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N475" s="3">
@@ -31814,7 +31820,7 @@
         <v>183</v>
       </c>
       <c r="M476" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N476" s="3">
@@ -31861,7 +31867,7 @@
         <v>19</v>
       </c>
       <c r="M477" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N477" s="3">
@@ -31908,7 +31914,7 @@
         <v>183</v>
       </c>
       <c r="M478" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N478" s="3">
@@ -31955,7 +31961,7 @@
         <v>19</v>
       </c>
       <c r="M479" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N479" s="3">
@@ -32002,7 +32008,7 @@
         <v>19</v>
       </c>
       <c r="M480" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N480" s="3">
@@ -32049,7 +32055,7 @@
         <v>19</v>
       </c>
       <c r="M481" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N481" s="3">
@@ -32096,7 +32102,7 @@
         <v>19</v>
       </c>
       <c r="M482" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N482" s="3">
@@ -32143,7 +32149,7 @@
         <v>183</v>
       </c>
       <c r="M483" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N483" s="3">
@@ -32190,7 +32196,7 @@
         <v>25</v>
       </c>
       <c r="M484" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N484" s="3">
@@ -32237,7 +32243,7 @@
         <v>19</v>
       </c>
       <c r="M485" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N485" s="3">
@@ -32284,7 +32290,7 @@
         <v>183</v>
       </c>
       <c r="M486" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N486" s="3">
@@ -32331,7 +32337,7 @@
         <v>19</v>
       </c>
       <c r="M487" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N487" s="3">
@@ -32378,7 +32384,7 @@
         <v>19</v>
       </c>
       <c r="M488" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N488" s="3">
@@ -32425,7 +32431,7 @@
         <v>19</v>
       </c>
       <c r="M489" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N489" s="3">
@@ -32472,7 +32478,7 @@
         <v>19</v>
       </c>
       <c r="M490" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N490" s="3">
@@ -32519,7 +32525,7 @@
         <v>183</v>
       </c>
       <c r="M491" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N491" s="3">
@@ -32566,7 +32572,7 @@
         <v>19</v>
       </c>
       <c r="M492" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N492" s="3">
@@ -32613,7 +32619,7 @@
         <v>19</v>
       </c>
       <c r="M493" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N493" s="3">
@@ -32660,7 +32666,7 @@
         <v>183</v>
       </c>
       <c r="M494" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N494" s="3">
@@ -32707,7 +32713,7 @@
         <v>183</v>
       </c>
       <c r="M495" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N495" s="3">
@@ -32754,7 +32760,7 @@
         <v>183</v>
       </c>
       <c r="M496" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N496" s="3">
@@ -32801,7 +32807,7 @@
         <v>183</v>
       </c>
       <c r="M497" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N497" s="3">
@@ -32848,7 +32854,7 @@
         <v>183</v>
       </c>
       <c r="M498" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N498" s="3">
@@ -32895,7 +32901,7 @@
         <v>19</v>
       </c>
       <c r="M499" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N499" s="3">
@@ -32942,7 +32948,7 @@
         <v>183</v>
       </c>
       <c r="M500" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N500" s="3">
@@ -32989,7 +32995,7 @@
         <v>183</v>
       </c>
       <c r="M501" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N501" s="3">
@@ -33036,7 +33042,7 @@
         <v>19</v>
       </c>
       <c r="M502" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N502" s="3">
@@ -33083,7 +33089,7 @@
         <v>19</v>
       </c>
       <c r="M503" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N503" s="3">
@@ -33130,7 +33136,7 @@
         <v>19</v>
       </c>
       <c r="M504" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N504" s="3">
@@ -33177,7 +33183,7 @@
         <v>183</v>
       </c>
       <c r="M505" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N505" s="3">
@@ -33224,7 +33230,7 @@
         <v>183</v>
       </c>
       <c r="M506" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N506" s="3">
@@ -33271,7 +33277,7 @@
         <v>183</v>
       </c>
       <c r="M507" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N507" s="3">
@@ -33318,7 +33324,7 @@
         <v>25</v>
       </c>
       <c r="M508" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N508" s="3">
@@ -33365,7 +33371,7 @@
         <v>25</v>
       </c>
       <c r="M509" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N509" s="3">
@@ -33412,7 +33418,7 @@
         <v>183</v>
       </c>
       <c r="M510" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N510" s="3">
@@ -33459,7 +33465,7 @@
         <v>19</v>
       </c>
       <c r="M511" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N511" s="3">
@@ -33506,7 +33512,7 @@
         <v>19</v>
       </c>
       <c r="M512" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N512" s="3">
@@ -33553,7 +33559,7 @@
         <v>25</v>
       </c>
       <c r="M513" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N513" s="3">
@@ -33600,7 +33606,7 @@
         <v>19</v>
       </c>
       <c r="M514" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N514" s="3">
@@ -33647,7 +33653,7 @@
         <v>25</v>
       </c>
       <c r="M515" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N515" s="3">
@@ -33694,7 +33700,7 @@
         <v>19</v>
       </c>
       <c r="M516" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N516" s="3">
@@ -33741,7 +33747,7 @@
         <v>183</v>
       </c>
       <c r="M517" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N517" s="3">
@@ -33788,7 +33794,7 @@
         <v>25</v>
       </c>
       <c r="M518" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N518" s="3">
@@ -33835,7 +33841,7 @@
         <v>183</v>
       </c>
       <c r="M519" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N519" s="3">
@@ -33882,7 +33888,7 @@
         <v>25</v>
       </c>
       <c r="M520" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N520" s="3">
@@ -33929,7 +33935,7 @@
         <v>19</v>
       </c>
       <c r="M521" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N521" s="3">
@@ -33976,7 +33982,7 @@
         <v>19</v>
       </c>
       <c r="M522" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N522" s="3">
@@ -34023,7 +34029,7 @@
         <v>25</v>
       </c>
       <c r="M523" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N523" s="3">
@@ -34070,7 +34076,7 @@
         <v>25</v>
       </c>
       <c r="M524" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N524" s="3">
@@ -34117,7 +34123,7 @@
         <v>19</v>
       </c>
       <c r="M525" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N525" s="3">
@@ -34164,7 +34170,7 @@
         <v>19</v>
       </c>
       <c r="M526" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N526" s="3">
@@ -34211,7 +34217,7 @@
         <v>19</v>
       </c>
       <c r="M527" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N527" s="3">
@@ -34258,7 +34264,7 @@
         <v>183</v>
       </c>
       <c r="M528" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N528" s="3">
@@ -34305,7 +34311,7 @@
         <v>25</v>
       </c>
       <c r="M529" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N529" s="3">
@@ -34352,7 +34358,7 @@
         <v>19</v>
       </c>
       <c r="M530" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N530" s="3">
@@ -34399,7 +34405,7 @@
         <v>25</v>
       </c>
       <c r="M531" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N531" s="3">
@@ -34446,7 +34452,7 @@
         <v>25</v>
       </c>
       <c r="M532" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N532" s="3">
@@ -34493,7 +34499,7 @@
         <v>25</v>
       </c>
       <c r="M533" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N533" s="3">
@@ -34540,7 +34546,7 @@
         <v>19</v>
       </c>
       <c r="M534" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N534" s="3">
@@ -34587,7 +34593,7 @@
         <v>25</v>
       </c>
       <c r="M535" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N535" s="3">
@@ -34634,7 +34640,7 @@
         <v>19</v>
       </c>
       <c r="M536" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N536" s="3">
@@ -34681,7 +34687,7 @@
         <v>19</v>
       </c>
       <c r="M537" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N537" s="3">
@@ -34728,7 +34734,7 @@
         <v>25</v>
       </c>
       <c r="M538" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N538" s="3">
@@ -34775,7 +34781,7 @@
         <v>19</v>
       </c>
       <c r="M539" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N539" s="3">
@@ -34822,7 +34828,7 @@
         <v>19</v>
       </c>
       <c r="M540" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N540" s="3">
@@ -34869,7 +34875,7 @@
         <v>183</v>
       </c>
       <c r="M541" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N541" s="3">
@@ -34916,7 +34922,7 @@
         <v>183</v>
       </c>
       <c r="M542" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N542" s="3">
@@ -34963,7 +34969,7 @@
         <v>19</v>
       </c>
       <c r="M543" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N543" s="3">
@@ -35010,7 +35016,7 @@
         <v>183</v>
       </c>
       <c r="M544" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N544" s="3">
@@ -35057,7 +35063,7 @@
         <v>25</v>
       </c>
       <c r="M545" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N545" s="3">
@@ -35104,7 +35110,7 @@
         <v>19</v>
       </c>
       <c r="M546" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N546" s="3">
@@ -35151,7 +35157,7 @@
         <v>25</v>
       </c>
       <c r="M547" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N547" s="3">
@@ -35198,7 +35204,7 @@
         <v>19</v>
       </c>
       <c r="M548" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N548" s="3">
@@ -35245,7 +35251,7 @@
         <v>183</v>
       </c>
       <c r="M549" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N549" s="3">
@@ -35292,7 +35298,7 @@
         <v>19</v>
       </c>
       <c r="M550" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N550" s="3">
@@ -35339,7 +35345,7 @@
         <v>25</v>
       </c>
       <c r="M551" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N551" s="3">
@@ -35386,7 +35392,7 @@
         <v>183</v>
       </c>
       <c r="M552" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N552" s="3">
@@ -35433,7 +35439,7 @@
         <v>19</v>
       </c>
       <c r="M553" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N553" s="3">
@@ -35480,7 +35486,7 @@
         <v>183</v>
       </c>
       <c r="M554" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N554" s="3">
@@ -35527,7 +35533,7 @@
         <v>25</v>
       </c>
       <c r="M555" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N555" s="3">
@@ -35574,7 +35580,7 @@
         <v>25</v>
       </c>
       <c r="M556" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N556" s="3">
@@ -35621,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="M557" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N557" s="3">
@@ -35668,7 +35674,7 @@
         <v>19</v>
       </c>
       <c r="M558" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N558" s="3">
@@ -35715,7 +35721,7 @@
         <v>25</v>
       </c>
       <c r="M559" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N559" s="3">
@@ -35762,7 +35768,7 @@
         <v>19</v>
       </c>
       <c r="M560" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N560" s="3">
@@ -35809,7 +35815,7 @@
         <v>25</v>
       </c>
       <c r="M561" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N561" s="3">
@@ -35856,7 +35862,7 @@
         <v>19</v>
       </c>
       <c r="M562" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N562" s="3">
@@ -35903,7 +35909,7 @@
         <v>183</v>
       </c>
       <c r="M563" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N563" s="3">
@@ -35950,7 +35956,7 @@
         <v>19</v>
       </c>
       <c r="M564" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N564" s="3">
@@ -35997,7 +36003,7 @@
         <v>183</v>
       </c>
       <c r="M565" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N565" s="3">
@@ -36044,7 +36050,7 @@
         <v>25</v>
       </c>
       <c r="M566" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N566" s="3">
@@ -36091,7 +36097,7 @@
         <v>19</v>
       </c>
       <c r="M567" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N567" s="3">
@@ -36138,7 +36144,7 @@
         <v>183</v>
       </c>
       <c r="M568" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N568" s="3">
@@ -36185,7 +36191,7 @@
         <v>183</v>
       </c>
       <c r="M569" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N569" s="3">
@@ -36232,7 +36238,7 @@
         <v>19</v>
       </c>
       <c r="M570" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N570" s="3">
@@ -36279,7 +36285,7 @@
         <v>25</v>
       </c>
       <c r="M571" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N571" s="3">
@@ -36326,7 +36332,7 @@
         <v>183</v>
       </c>
       <c r="M572" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N572" s="3">
@@ -36373,7 +36379,7 @@
         <v>183</v>
       </c>
       <c r="M573" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N573" s="3">
@@ -36420,7 +36426,7 @@
         <v>2351</v>
       </c>
       <c r="M574" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N574" s="3">
@@ -36467,7 +36473,7 @@
         <v>19</v>
       </c>
       <c r="M575" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N575" s="3">
@@ -36514,7 +36520,7 @@
         <v>19</v>
       </c>
       <c r="M576" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N576" s="3">
@@ -36561,7 +36567,7 @@
         <v>183</v>
       </c>
       <c r="M577" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N577" s="3">
@@ -36608,7 +36614,7 @@
         <v>19</v>
       </c>
       <c r="M578" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N578" s="3">
@@ -36655,7 +36661,7 @@
         <v>19</v>
       </c>
       <c r="M579" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N579" s="3">
@@ -36702,7 +36708,7 @@
         <v>183</v>
       </c>
       <c r="M580" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N580" s="3">
@@ -36749,7 +36755,7 @@
         <v>19</v>
       </c>
       <c r="M581" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N581" s="3">
@@ -36796,7 +36802,7 @@
         <v>25</v>
       </c>
       <c r="M582" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N582" s="3">
@@ -36843,7 +36849,7 @@
         <v>19</v>
       </c>
       <c r="M583" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N583" s="3">
@@ -36890,7 +36896,7 @@
         <v>25</v>
       </c>
       <c r="M584" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N584" s="3">
@@ -36937,7 +36943,7 @@
         <v>183</v>
       </c>
       <c r="M585" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N585" s="3">
@@ -36984,7 +36990,7 @@
         <v>19</v>
       </c>
       <c r="M586" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N586" s="3">
@@ -37031,7 +37037,7 @@
         <v>19</v>
       </c>
       <c r="M587" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N587" s="3">
@@ -37078,7 +37084,7 @@
         <v>19</v>
       </c>
       <c r="M588" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N588" s="3">
@@ -37125,7 +37131,7 @@
         <v>19</v>
       </c>
       <c r="M589" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N589" s="3">
@@ -37172,7 +37178,7 @@
         <v>25</v>
       </c>
       <c r="M590" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N590" s="3">
@@ -37219,7 +37225,7 @@
         <v>25</v>
       </c>
       <c r="M591" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N591" s="3">
@@ -37266,7 +37272,7 @@
         <v>25</v>
       </c>
       <c r="M592" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N592" s="3">
@@ -37313,7 +37319,7 @@
         <v>183</v>
       </c>
       <c r="M593" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N593" s="3">
@@ -37360,7 +37366,7 @@
         <v>19</v>
       </c>
       <c r="M594" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N594" s="3">
@@ -37407,7 +37413,7 @@
         <v>19</v>
       </c>
       <c r="M595" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N595" s="3">
@@ -37454,7 +37460,7 @@
         <v>19</v>
       </c>
       <c r="M596" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N596" s="3">
@@ -37501,7 +37507,7 @@
         <v>25</v>
       </c>
       <c r="M597" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N597" s="3">
@@ -37548,7 +37554,7 @@
         <v>19</v>
       </c>
       <c r="M598" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N598" s="3">
@@ -37595,7 +37601,7 @@
         <v>19</v>
       </c>
       <c r="M599" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N599" s="3">
@@ -37642,7 +37648,7 @@
         <v>183</v>
       </c>
       <c r="M600" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N600" s="3">
@@ -37689,7 +37695,7 @@
         <v>183</v>
       </c>
       <c r="M601" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N601" s="3">
@@ -37736,7 +37742,7 @@
         <v>19</v>
       </c>
       <c r="M602" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N602" s="3">
@@ -37783,7 +37789,7 @@
         <v>25</v>
       </c>
       <c r="M603" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N603" s="3">
@@ -37830,7 +37836,7 @@
         <v>19</v>
       </c>
       <c r="M604" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N604" s="3">
@@ -37877,7 +37883,7 @@
         <v>19</v>
       </c>
       <c r="M605" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N605" s="3">
@@ -37924,7 +37930,7 @@
         <v>183</v>
       </c>
       <c r="M606" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N606" s="3">
@@ -37971,7 +37977,7 @@
         <v>25</v>
       </c>
       <c r="M607" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N607" s="3">
@@ -38018,7 +38024,7 @@
         <v>25</v>
       </c>
       <c r="M608" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N608" s="3">
@@ -38065,7 +38071,7 @@
         <v>25</v>
       </c>
       <c r="M609" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N609" s="3">
@@ -38112,7 +38118,7 @@
         <v>25</v>
       </c>
       <c r="M610" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N610" s="3">
@@ -38159,7 +38165,7 @@
         <v>183</v>
       </c>
       <c r="M611" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N611" s="3">
@@ -38206,7 +38212,7 @@
         <v>183</v>
       </c>
       <c r="M612" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N612" s="3">
@@ -38253,7 +38259,7 @@
         <v>183</v>
       </c>
       <c r="M613" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N613" s="3">
@@ -38300,7 +38306,7 @@
         <v>183</v>
       </c>
       <c r="M614" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N614" s="3">
@@ -38347,7 +38353,7 @@
         <v>25</v>
       </c>
       <c r="M615" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N615" s="3">
@@ -38394,7 +38400,7 @@
         <v>19</v>
       </c>
       <c r="M616" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N616" s="3">
@@ -38441,7 +38447,7 @@
         <v>19</v>
       </c>
       <c r="M617" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N617" s="3">
@@ -38488,7 +38494,7 @@
         <v>2528</v>
       </c>
       <c r="M618" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N618" s="3">
@@ -38535,7 +38541,7 @@
         <v>183</v>
       </c>
       <c r="M619" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N619" s="3">
@@ -38582,7 +38588,7 @@
         <v>25</v>
       </c>
       <c r="M620" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N620" s="3">
@@ -38629,7 +38635,7 @@
         <v>25</v>
       </c>
       <c r="M621" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N621" s="3">
@@ -38676,7 +38682,7 @@
         <v>183</v>
       </c>
       <c r="M622" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N622" s="3">
@@ -38723,7 +38729,7 @@
         <v>19</v>
       </c>
       <c r="M623" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N623" s="3">
@@ -38770,7 +38776,7 @@
         <v>19</v>
       </c>
       <c r="M624" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N624" s="3">
@@ -38817,7 +38823,7 @@
         <v>19</v>
       </c>
       <c r="M625" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N625" s="3">
@@ -38864,7 +38870,7 @@
         <v>25</v>
       </c>
       <c r="M626" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N626" s="3">
@@ -38911,7 +38917,7 @@
         <v>19</v>
       </c>
       <c r="M627" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N627" s="3">
@@ -38958,7 +38964,7 @@
         <v>25</v>
       </c>
       <c r="M628" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N628" s="3">
@@ -39005,7 +39011,7 @@
         <v>19</v>
       </c>
       <c r="M629" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N629" s="3">
@@ -39052,7 +39058,7 @@
         <v>25</v>
       </c>
       <c r="M630" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N630" s="3">
@@ -39099,7 +39105,7 @@
         <v>25</v>
       </c>
       <c r="M631" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N631" s="3">
@@ -39146,7 +39152,7 @@
         <v>19</v>
       </c>
       <c r="M632" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N632" s="3">
@@ -39193,7 +39199,7 @@
         <v>19</v>
       </c>
       <c r="M633" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N633" s="3">
@@ -39240,7 +39246,7 @@
         <v>183</v>
       </c>
       <c r="M634" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N634" s="3">
@@ -39287,7 +39293,7 @@
         <v>183</v>
       </c>
       <c r="M635" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N635" s="3">
@@ -39334,7 +39340,7 @@
         <v>2602</v>
       </c>
       <c r="M636" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N636" s="3">
@@ -39381,7 +39387,7 @@
         <v>19</v>
       </c>
       <c r="M637" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N637" s="3">
@@ -39428,7 +39434,7 @@
         <v>19</v>
       </c>
       <c r="M638" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N638" s="3">
@@ -39475,7 +39481,7 @@
         <v>183</v>
       </c>
       <c r="M639" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N639" s="3">
@@ -39522,7 +39528,7 @@
         <v>183</v>
       </c>
       <c r="M640" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N640" s="3">
@@ -39569,7 +39575,7 @@
         <v>19</v>
       </c>
       <c r="M641" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N641" s="3">
@@ -39597,7 +39603,7 @@
         <v>2625</v>
       </c>
       <c r="G642" s="2">
-        <f t="shared" ref="G642:G705" si="21">VALUE(F642)</f>
+        <f t="shared" ref="G642:G701" si="21">VALUE(F642)</f>
         <v>9850185649</v>
       </c>
       <c r="H642" s="2" t="s">
@@ -39616,7 +39622,7 @@
         <v>25</v>
       </c>
       <c r="M642" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N642" s="3">
@@ -39663,7 +39669,7 @@
         <v>19</v>
       </c>
       <c r="M643" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N643" s="3">
@@ -39710,7 +39716,7 @@
         <v>19</v>
       </c>
       <c r="M644" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N644" s="3">
@@ -39757,7 +39763,7 @@
         <v>19</v>
       </c>
       <c r="M645" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N645" s="3">
@@ -39804,7 +39810,7 @@
         <v>183</v>
       </c>
       <c r="M646" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N646" s="3">
@@ -39851,7 +39857,7 @@
         <v>19</v>
       </c>
       <c r="M647" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N647" s="3">
@@ -39898,7 +39904,7 @@
         <v>183</v>
       </c>
       <c r="M648" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N648" s="3">
@@ -39945,7 +39951,7 @@
         <v>183</v>
       </c>
       <c r="M649" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N649" s="3">
@@ -39992,7 +39998,7 @@
         <v>25</v>
       </c>
       <c r="M650" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N650" s="3">
@@ -40039,7 +40045,7 @@
         <v>19</v>
       </c>
       <c r="M651" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N651" s="3">
@@ -40086,7 +40092,7 @@
         <v>19</v>
       </c>
       <c r="M652" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N652" s="3">
@@ -40133,7 +40139,7 @@
         <v>25</v>
       </c>
       <c r="M653" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N653" s="3">
@@ -40180,7 +40186,7 @@
         <v>183</v>
       </c>
       <c r="M654" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N654" s="3">
@@ -40227,7 +40233,7 @@
         <v>183</v>
       </c>
       <c r="M655" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N655" s="3">
@@ -40274,7 +40280,7 @@
         <v>25</v>
       </c>
       <c r="M656" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N656" s="3">
@@ -40321,7 +40327,7 @@
         <v>25</v>
       </c>
       <c r="M657" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N657" s="3">
@@ -40368,7 +40374,7 @@
         <v>25</v>
       </c>
       <c r="M658" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N658" s="3">
@@ -40415,7 +40421,7 @@
         <v>183</v>
       </c>
       <c r="M659" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N659" s="3">
@@ -40462,7 +40468,7 @@
         <v>19</v>
       </c>
       <c r="M660" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N660" s="3">
@@ -40509,7 +40515,7 @@
         <v>19</v>
       </c>
       <c r="M661" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N661" s="3">
@@ -40556,7 +40562,7 @@
         <v>25</v>
       </c>
       <c r="M662" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N662" s="3">
@@ -40603,7 +40609,7 @@
         <v>19</v>
       </c>
       <c r="M663" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N663" s="3">
@@ -40650,7 +40656,7 @@
         <v>25</v>
       </c>
       <c r="M664" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N664" s="3">
@@ -40697,7 +40703,7 @@
         <v>25</v>
       </c>
       <c r="M665" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N665" s="3">
@@ -40744,7 +40750,7 @@
         <v>25</v>
       </c>
       <c r="M666" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N666" s="3">
@@ -40791,7 +40797,7 @@
         <v>183</v>
       </c>
       <c r="M667" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N667" s="3">
@@ -40838,7 +40844,7 @@
         <v>25</v>
       </c>
       <c r="M668" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N668" s="3">
@@ -40885,7 +40891,7 @@
         <v>19</v>
       </c>
       <c r="M669" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N669" s="3">
@@ -40932,7 +40938,7 @@
         <v>25</v>
       </c>
       <c r="M670" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N670" s="3">
@@ -40979,7 +40985,7 @@
         <v>19</v>
       </c>
       <c r="M671" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N671" s="3">
@@ -41026,7 +41032,7 @@
         <v>183</v>
       </c>
       <c r="M672" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N672" s="3">
@@ -41073,7 +41079,7 @@
         <v>25</v>
       </c>
       <c r="M673" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N673" s="3">
@@ -41120,7 +41126,7 @@
         <v>25</v>
       </c>
       <c r="M674" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N674" s="3">
@@ -41167,7 +41173,7 @@
         <v>25</v>
       </c>
       <c r="M675" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N675" s="3">
@@ -41214,7 +41220,7 @@
         <v>183</v>
       </c>
       <c r="M676" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N676" s="3">
@@ -41261,7 +41267,7 @@
         <v>183</v>
       </c>
       <c r="M677" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N677" s="3">
@@ -41308,7 +41314,7 @@
         <v>183</v>
       </c>
       <c r="M678" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N678" s="3">
@@ -41355,7 +41361,7 @@
         <v>19</v>
       </c>
       <c r="M679" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N679" s="3">
@@ -41402,7 +41408,7 @@
         <v>25</v>
       </c>
       <c r="M680" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N680" s="3">
@@ -41449,7 +41455,7 @@
         <v>25</v>
       </c>
       <c r="M681" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N681" s="3">
@@ -41496,7 +41502,7 @@
         <v>19</v>
       </c>
       <c r="M682" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N682" s="3">
@@ -41543,7 +41549,7 @@
         <v>25</v>
       </c>
       <c r="M683" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N683" s="3">
@@ -41590,7 +41596,7 @@
         <v>25</v>
       </c>
       <c r="M684" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N684" s="3">
@@ -41637,7 +41643,7 @@
         <v>183</v>
       </c>
       <c r="M685" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N685" s="3">
@@ -41684,7 +41690,7 @@
         <v>183</v>
       </c>
       <c r="M686" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N686" s="3">
@@ -41731,7 +41737,7 @@
         <v>183</v>
       </c>
       <c r="M687" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N687" s="3">
@@ -41778,7 +41784,7 @@
         <v>19</v>
       </c>
       <c r="M688" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N688" s="3">
@@ -41825,7 +41831,7 @@
         <v>19</v>
       </c>
       <c r="M689" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N689" s="3">
@@ -41872,7 +41878,7 @@
         <v>25</v>
       </c>
       <c r="M690" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N690" s="3">
@@ -41919,7 +41925,7 @@
         <v>19</v>
       </c>
       <c r="M691" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N691" s="3">
@@ -41966,7 +41972,7 @@
         <v>19</v>
       </c>
       <c r="M692" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N692" s="3">
@@ -42013,7 +42019,7 @@
         <v>25</v>
       </c>
       <c r="M693" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N693" s="3">
@@ -42060,7 +42066,7 @@
         <v>19</v>
       </c>
       <c r="M694" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N694" s="3">
@@ -42107,7 +42113,7 @@
         <v>183</v>
       </c>
       <c r="M695" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N695" s="3">
@@ -42154,7 +42160,7 @@
         <v>25</v>
       </c>
       <c r="M696" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N696" s="3">
@@ -42201,7 +42207,7 @@
         <v>19</v>
       </c>
       <c r="M697" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N697" s="3">
@@ -42248,7 +42254,7 @@
         <v>19</v>
       </c>
       <c r="M698" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Bronze</v>
       </c>
       <c r="N698" s="3">
@@ -42295,7 +42301,7 @@
         <v>25</v>
       </c>
       <c r="M699" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N699" s="3">
@@ -42342,7 +42348,7 @@
         <v>183</v>
       </c>
       <c r="M700" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Gold</v>
       </c>
       <c r="N700" s="3">
@@ -42389,7 +42395,7 @@
         <v>25</v>
       </c>
       <c r="M701" s="2" t="str">
-        <f>_xlfn.XLOOKUP(TRIM(Table1[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
+        <f>_xlfn.XLOOKUP(TRIM(Customer[[#This Row],[Membership]]),Data_Profiling!$A$2:$A$7,Data_Profiling!$B$2:$B$7,"Checkmanually")</f>
         <v>Silver</v>
       </c>
       <c r="N701" s="3">
@@ -42503,6 +42509,9 @@
       <c r="B11" t="s">
         <v>2875</v>
       </c>
+      <c r="D11" t="s">
+        <v>2882</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -42513,6 +42522,9 @@
       </c>
       <c r="C12" t="s">
         <v>2878</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2883</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
